--- a/dataset/01.w_Defects/uninit_pointer.xlsx
+++ b/dataset/01.w_Defects/uninit_pointer.xlsx
@@ -781,7 +781,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>char ** uninit_pointer_016_gbl_doubleptr; uninit_pointer_014_s_001 *s; TWO } values; extern volatile int vflag; void uninit_pointer_016() { int flag=0,i; char *s=(char*) malloc(10*sizeof(char)); if(uninit_pointer_016_func_001(flag)==0) { uninit_pointer_016_func_002(); } if(uninit_pointer_016_gbl_doubleptr!=NULL) { for(i=0;i&lt;10;i++) { if(uninit_pointer_016_gbl_doubleptr[i] !=NULL) { if(i==7) strcpy(s,uninit_pointer_016_gbl_doubleptr[i]);/*Tool should detect this line as error*/ /*ERROR:Uninitialized pointer*/ free (uninit_pointer_016_gbl_doubleptr[i]); } } free(uninit_pointer_016_gbl_doubleptr); free(s); } } void uninit_pointer_016_func_002() { int i; if(uninit_pointer_016_func_001(0)==0) { uninit_pointer_016_gbl_doubleptr=(char**) malloc(10*sizeof(char*)); for(i=0;i&lt;10;i++) { uninit_pointer_016_gbl_doubleptr[i]=(char*) malloc(10*sizeof(char)); if(i&lt;5) strcpy(uninit_pointer_016_gbl_doubleptr[i],"STRING00"); } } } int uninit_pointer_016_func_001(int flag) { int ret =0; if (flag ==0) ret = 0; else ret=1; return ret; }</t>
+          <t>char ** uninit_pointer_016_gbl_doubleptr; uninit_pointer_014_s_001 *s; TWO } values; extern volatile int vflag; void uninit_pointer_016() { int flag=0,i; char *s=(char*) malloc(10*sizeof(char)); if(uninit_pointer_016_func_001(flag)==0) { uninit_pointer_016_func_002(); } if(uninit_pointer_016_gbl_doubleptr!=NULL) { for(i=0;i&lt;10;i++) { if(uninit_pointer_016_gbl_doubleptr[i] !=NULL) { if(i==7) strcpy(s,uninit_pointer_016_gbl_doubleptr[i]);/*Tool should detect this line as error*/ /*ERROR:Uninitialized pointer*/ free (uninit_pointer_016_gbl_doubleptr[i]); } } free(uninit_pointer_016_gbl_doubleptr); free(s); } } int uninit_pointer_016_func_001(int flag) { int ret =0; if (flag ==0) ret = 0; else ret=1; return ret; } void uninit_pointer_016_func_002() { int i; if(uninit_pointer_016_func_001(0)==0) { uninit_pointer_016_gbl_doubleptr=(char**) malloc(10*sizeof(char*)); for(i=0;i&lt;10;i++) { uninit_pointer_016_gbl_doubleptr[i]=(char*) malloc(10*sizeof(char)); if(i&lt;5) strcpy(uninit_pointer_016_gbl_doubleptr[i],"STRING00"); } } }</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
